--- a/tests/resources/EVA_Submission_test_with_formula.xlsx
+++ b/tests/resources/EVA_Submission_test_with_formula.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nkumar2/PycharmProjects/eva-sub-cli/tests/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528BD9AF-8A30-DE4A-B1DA-E6CD600C8F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8376AF2-4EF5-B846-B113-01EB661A7D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21900" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21900" yWindow="-21000" windowWidth="38400" windowHeight="19980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLEASE READ FIRST" sheetId="1" r:id="rId1"/>
     <sheet name="Submitter Details" sheetId="2" r:id="rId2"/>
-    <sheet name="Data Acknowledgement" sheetId="12" r:id="rId3"/>
+    <sheet name="Statements" sheetId="12" r:id="rId3"/>
     <sheet name="Project HELP" sheetId="3" r:id="rId4"/>
     <sheet name="Project" sheetId="4" r:id="rId5"/>
     <sheet name="Analysis HELP" sheetId="5" r:id="rId6"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="603">
   <si>
     <t>PLEASE READ FIRST</t>
   </si>
@@ -1854,6 +1854,9 @@
   </si>
   <si>
     <t>To the best of my knowledge, the data being submitted are not subject to any restrictions that prohibit their open sharing and are submitted in compliance with applicable national and international access and benefit-sharing obligations, in accordance with the EMBL-EBI Terms of Use (https://www.ebi.ac.uk/about/terms-of-use/).</t>
+  </si>
+  <si>
+    <t>Statements</t>
   </si>
 </sst>
 </file>
@@ -6967,7 +6970,7 @@
     </row>
     <row r="14" spans="1:1025" ht="60" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B14" s="65" t="s">
         <v>597</v>
@@ -8057,7 +8060,7 @@
       <c r="AMK24" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bxpGWfjM9E10gpnOm+nh/3+cDcUIyllZFKvqt2Z8uwCVF/WTQrhozPwYS63scLX6sXYmpO/NQpOIRitwZVw/Zw==" saltValue="pWMkJT7/tjC0PP2FS93QKA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="flxGqJvNE+qXKYkA039PIXjU2hPt+ZimWhzvuwRrUFx8GEsvKbKpg12bI2ZT1vXm+EMAdb011efYBu4fGk7mnw==" saltValue="AlG6mhOehPLZkqHwhVwBjw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>

--- a/tests/resources/EVA_Submission_test_with_formula.xlsx
+++ b/tests/resources/EVA_Submission_test_with_formula.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8376AF2-4EF5-B846-B113-01EB661A7D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21900" yWindow="-21000" windowWidth="38400" windowHeight="19980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLEASE READ FIRST" sheetId="1" r:id="rId1"/>
@@ -2435,11 +2435,17 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2453,14 +2459,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2468,14 +2468,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2774,10 +2774,10 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:1025" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="72"/>
+      <c r="B2" s="74"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2786,10 +2786,10 @@
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="75" t="s">
         <v>598</v>
       </c>
-      <c r="B3" s="73"/>
+      <c r="B3" s="75"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -2798,10 +2798,10 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="74"/>
+      <c r="B4" s="76"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2810,10 +2810,10 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="75"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -4890,10 +4890,10 @@
       <c r="AMK8" s="5"/>
     </row>
     <row r="9" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="77"/>
+      <c r="B9" s="72"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -6946,10 +6946,10 @@
       <c r="AMK10" s="5"/>
     </row>
     <row r="11" spans="1:1025" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="78"/>
+      <c r="B11" s="73"/>
     </row>
     <row r="12" spans="1:1025" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
@@ -7009,28 +7009,28 @@
       </c>
     </row>
     <row r="20" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="76"/>
+      <c r="B20" s="70"/>
     </row>
     <row r="21" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="76"/>
+      <c r="B21" s="70"/>
     </row>
     <row r="22" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="76"/>
+      <c r="B22" s="70"/>
     </row>
     <row r="23" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="76"/>
+      <c r="B23" s="70"/>
     </row>
     <row r="24" spans="1:1025" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
@@ -8062,6 +8062,11 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="flxGqJvNE+qXKYkA039PIXjU2hPt+ZimWhzvuwRrUFx8GEsvKbKpg12bI2ZT1vXm+EMAdb011efYBu4fGk7mnw==" saltValue="AlG6mhOehPLZkqHwhVwBjw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
@@ -8070,11 +8075,6 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9950,10 +9950,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="47" x14ac:dyDescent="0.2">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="78" t="s">
         <v>596</v>
       </c>
-      <c r="B1" s="70"/>
+      <c r="B1" s="78"/>
     </row>
     <row r="2" spans="1:2" s="67" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="66" t="s">
@@ -11100,10 +11100,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="83" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="83"/>
       <c r="C1" s="79"/>
       <c r="D1" s="43" t="s">
         <v>217</v>
@@ -11169,16 +11169,16 @@
       <c r="I2" s="82"/>
       <c r="J2" s="82"/>
       <c r="K2" s="82"/>
-      <c r="L2" s="83" t="s">
+      <c r="L2" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83" t="s">
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81" t="s">
         <v>144</v>
       </c>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
       <c r="R2" s="82" t="s">
         <v>151</v>
       </c>
@@ -11422,16 +11422,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="Z2:AI2"/>
     <mergeCell ref="AJ2:AS2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="L2:N2"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Metadata and VCF" prompt="These sample names must match those provided in the VCF file(s)" sqref="E1 B4:B1003" xr:uid="{00000000-0002-0000-0700-000000000000}">
